--- a/site/HR-ITSM-HaloITSM-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-HaloITSM-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,336 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Key Functions</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>h_01KX5W503G05NTZR0JWB389FK1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5W503G05NTZR0JWB389FK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>h_01KX5WDWP688V7XFZWPZTN63ES</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5WDWP688V7XFZWPZTN63ES</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Integration Setup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01KX5WGST12AK0FJE5XVCA9F46</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5WGST12AK0FJE5XVCA9F46</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Create Integration</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01KX5WHHFRW3D448HA6X90Y17S</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5WHHFRW3D448HA6X90Y17S</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01KX5WMN2YYAKY00R6B4KMKV7V</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5WMN2YYAKY00R6B4KMKV7V</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Features</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01KX5WNEEEFHD29J0XVYATH04E</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5WNEEEFHD29J0XVYATH04E</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Service Desk Bridge</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01KW1TH82EGE4EW275DJSB2X28</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KW1TH82EGE4EW275DJSB2X28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01KX5WPEVC7F8NRR30ZTDR2W4H</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5WPEVC7F8NRR30ZTDR2W4H</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Application Settings</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KX5X4PVEA00R9NTDJXB85JR9</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5X4PVEA00R9NTDJXB85JR9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Filter Employees</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KX5X7FS4CCFGNCVBDMA6G43W</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5X7FS4CCFGNCVBDMA6G43W</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Employee Filter Configuration</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KX5XGS3JYFGVW1Q84RREW12P</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5XGS3JYFGVW1Q84RREW12P</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Service Desk</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KX5ZKWBXTX162GAE289HZ9MT</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5ZKWBXTX162GAE289HZ9MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KX60P5NX00Z4VSPJJJY6P88Z</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX60P5NX00Z4VSPJJJY6P88Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>JML Ticket Creation</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KX61939S4SZ5BEVCQHTG9E7H</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX61939S4SZ5BEVCQHTG9E7H</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TIcket Creation Configuration</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KX62FZ36XZ8CYT2AKJYB3PBY</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX62FZ36XZ8CYT2AKJYB3PBY</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/HR-ITSM-HaloITSM-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-HaloITSM-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,6 +790,358 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KXD24R6KTK64TSFZQ15WSWQC</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD24R6KTK64TSFZQ15WSWQC</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KXD2651GJMQ6D9TWKV4SSSP3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD2651GJMQ6D9TWKV4SSSP3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Define notification channel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KXD26T3P58PTGRVFB8TYXY4P</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD26T3P58PTGRVFB8TYXY4P</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Notification Configuration</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KXD29HX4PNGN0WXCW65Q1XRH</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD29HX4PNGN0WXCW65Q1XRH</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Global Operational Settings</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KXD2QFV2YDHGWHC3WSPM2901</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD2QFV2YDHGWHC3WSPM2901</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Logging Settings</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KXD2TCEBQ7ZZR8FH8MDKYFAY</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD2TCEBQ7ZZR8FH8MDKYFAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KXD2WYEFJZWHVJ7J2HGG6R6Q</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD2WYEFJZWHVJ7J2HGG6R6Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Log Insights Settings</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KXD3N3VJF9FQZ3SK744FQMJX</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD3N3VJF9FQZ3SK744FQMJX</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01KXD3P72ED6QQD6AFJXQMHSG5</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD3P72ED6QQD6AFJXQMHSG5</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Advanced Settings</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KXD3QARYZQSR9SSX7G475QJ4</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD3QARYZQSR9SSX7G475QJ4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Operation Safeguard Settings</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01KXD3X0JENXFZJ36P50T7KRF2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD3X0JENXFZJ36P50T7KRF2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Advanced Settings</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KXD4124NATJ17W8BA57FW3K4</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD4124NATJ17W8BA57FW3K4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KXD464107EABVR5YHHD9564T</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD464107EABVR5YHHD9564T</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/HR-ITSM-HaloITSM-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-HaloITSM-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,249 +705,249 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Service Desk</t>
+          <t>Filter Candidates</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KX5ZKWBXTX162GAE289HZ9MT</t>
+          <t>h_01KXJGJSM42FYWAZBX1WWC2KG5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5ZKWBXTX162GAE289HZ9MT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXJGJSM42FYWAZBX1WWC2KG5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Candidate Filter Configuration</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KX60P5NX00Z4VSPJJJY6P88Z</t>
+          <t>h_01KXJHWCDEMF3TSBV11RRWGG43</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX60P5NX00Z4VSPJJJY6P88Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXJHWCDEMF3TSBV11RRWGG43</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JML Ticket Creation</t>
+          <t>Service Desk</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KX61939S4SZ5BEVCQHTG9E7H</t>
+          <t>h_01KX5ZKWBXTX162GAE289HZ9MT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX61939S4SZ5BEVCQHTG9E7H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5ZKWBXTX162GAE289HZ9MT</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TIcket Creation Configuration</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KX62FZ36XZ8CYT2AKJYB3PBY</t>
+          <t>h_01KX60P5NX00Z4VSPJJJY6P88Z</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX62FZ36XZ8CYT2AKJYB3PBY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX60P5NX00Z4VSPJJJY6P88Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>ITSM Configuration</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KXD24R6KTK64TSFZQ15WSWQC</t>
+          <t>h_01KXJJN9VZBHQGB4Y7630BXC6D</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD24R6KTK64TSFZQ15WSWQC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXJJN9VZBHQGB4Y7630BXC6D</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Messaging Applications</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KXD2651GJMQ6D9TWKV4SSSP3</t>
+          <t>h_01KXJJXPJ1EWF19V6HRK6FT04W</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD2651GJMQ6D9TWKV4SSSP3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXJJXPJ1EWF19V6HRK6FT04W</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Define notification channel</t>
+          <t>JML Ticket Creation</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KXD26T3P58PTGRVFB8TYXY4P</t>
+          <t>h_01KX61939S4SZ5BEVCQHTG9E7H</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD26T3P58PTGRVFB8TYXY4P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX61939S4SZ5BEVCQHTG9E7H</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notification Configuration</t>
+          <t>Ticket Creation Configuration</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KXD29HX4PNGN0WXCW65Q1XRH</t>
+          <t>h_01KX62FZ36XZ8CYT2AKJYB3PBY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD29HX4PNGN0WXCW65Q1XRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX62FZ36XZ8CYT2AKJYB3PBY</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Global Operational Settings</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KXD2QFV2YDHGWHC3WSPM2901</t>
+          <t>h_01KXD24R6KTK64TSFZQ15WSWQC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD2QFV2YDHGWHC3WSPM2901</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD24R6KTK64TSFZQ15WSWQC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KXD2TCEBQ7ZZR8FH8MDKYFAY</t>
+          <t>h_01KXD2651GJMQ6D9TWKV4SSSP3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD2TCEBQ7ZZR8FH8MDKYFAY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD2651GJMQ6D9TWKV4SSSP3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Define notification channel</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KXD2WYEFJZWHVJ7J2HGG6R6Q</t>
+          <t>h_01KXD26T3P58PTGRVFB8TYXY4P</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD2WYEFJZWHVJ7J2HGG6R6Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD26T3P58PTGRVFB8TYXY4P</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Notification Configuration</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,63 +957,63 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KXD3N3VJF9FQZ3SK744FQMJX</t>
+          <t>h_01KXD29HX4PNGN0WXCW65Q1XRH</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD3N3VJF9FQZ3SK744FQMJX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD29HX4PNGN0WXCW65Q1XRH</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Global Operational Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KXD3P72ED6QQD6AFJXQMHSG5</t>
+          <t>h_01KXD2QFV2YDHGWHC3WSPM2901</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD3P72ED6QQD6AFJXQMHSG5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD2QFV2YDHGWHC3WSPM2901</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KXD3QARYZQSR9SSX7G475QJ4</t>
+          <t>h_01KXD2TCEBQ7ZZR8FH8MDKYFAY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD3QARYZQSR9SSX7G475QJ4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD2TCEBQ7ZZR8FH8MDKYFAY</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Operation Safeguard Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KXD3X0JENXFZJ36P50T7KRF2</t>
+          <t>h_01KXD2WYEFJZWHVJ7J2HGG6R6Q</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD3X0JENXFZJ36P50T7KRF2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD2WYEFJZWHVJ7J2HGG6R6Q</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,98 +1045,186 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KXD4124NATJ17W8BA57FW3K4</t>
+          <t>h_01KXD3N3VJF9FQZ3SK744FQMJX</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD4124NATJ17W8BA57FW3K4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD3N3VJF9FQZ3SK744FQMJX</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KXD464107EABVR5YHHD9564T</t>
+          <t>h_01KXD3P72ED6QQD6AFJXQMHSG5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD464107EABVR5YHHD9564T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD3P72ED6QQD6AFJXQMHSG5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>h_01KXD3QARYZQSR9SSX7G475QJ4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD3QARYZQSR9SSX7G475QJ4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Operation Safeguard Settings</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KXD3X0JENXFZJ36P50T7KRF2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD3X0JENXFZJ36P50T7KRF2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Advanced Settings</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01KXD4124NATJ17W8BA57FW3K4</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD4124NATJ17W8BA57FW3K4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01KXD464107EABVR5YHHD9564T</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD464107EABVR5YHHD9564T</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/HR-ITSM-HaloITSM-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-HaloITSM-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,29 +573,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Features</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01KX5WNEEEFHD29J0XVYATH04E</t>
+          <t>h_01KX5WPEVC7F8NRR30ZTDR2W4H</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5WNEEEFHD29J0XVYATH04E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5WPEVC7F8NRR30ZTDR2W4H</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Service Desk Bridge</t>
+          <t>Application Settings</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -605,63 +605,63 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KW1TH82EGE4EW275DJSB2X28</t>
+          <t>h_01KX5X4PVEA00R9NTDJXB85JR9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KW1TH82EGE4EW275DJSB2X28</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5X4PVEA00R9NTDJXB85JR9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Filter Employees</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KX5WPEVC7F8NRR30ZTDR2W4H</t>
+          <t>h_01KX5X7FS4CCFGNCVBDMA6G43W</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5WPEVC7F8NRR30ZTDR2W4H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5X7FS4CCFGNCVBDMA6G43W</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Application Settings</t>
+          <t>Employee Filter Configuration</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KX5X4PVEA00R9NTDJXB85JR9</t>
+          <t>h_01KX5XGS3JYFGVW1Q84RREW12P</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5X4PVEA00R9NTDJXB85JR9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5XGS3JYFGVW1Q84RREW12P</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Filter Employees</t>
+          <t>Filter Candidates</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KX5X7FS4CCFGNCVBDMA6G43W</t>
+          <t>h_01KXJGJSM42FYWAZBX1WWC2KG5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5X7FS4CCFGNCVBDMA6G43W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXJGJSM42FYWAZBX1WWC2KG5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Employee Filter Configuration</t>
+          <t>Candidate Lifecycle Configuration</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,129 +693,129 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KX5XGS3JYFGVW1Q84RREW12P</t>
+          <t>h_01KXJHWCDEMF3TSBV11RRWGG43</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5XGS3JYFGVW1Q84RREW12P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXJHWCDEMF3TSBV11RRWGG43</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Filter Candidates</t>
+          <t>Service Desk</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KXJGJSM42FYWAZBX1WWC2KG5</t>
+          <t>h_01KX5ZKWBXTX162GAE289HZ9MT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXJGJSM42FYWAZBX1WWC2KG5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5ZKWBXTX162GAE289HZ9MT</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Candidate Filter Configuration</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KXJHWCDEMF3TSBV11RRWGG43</t>
+          <t>h_01KX60P5NX00Z4VSPJJJY6P88Z</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXJHWCDEMF3TSBV11RRWGG43</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX60P5NX00Z4VSPJJJY6P88Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Service Desk</t>
+          <t>ITSM Configuration</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KX5ZKWBXTX162GAE289HZ9MT</t>
+          <t>h_01KXJJN9VZBHQGB4Y7630BXC6D</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX5ZKWBXTX162GAE289HZ9MT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXJJN9VZBHQGB4Y7630BXC6D</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Messaging Applications</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KX60P5NX00Z4VSPJJJY6P88Z</t>
+          <t>h_01KXJJXPJ1EWF19V6HRK6FT04W</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX60P5NX00Z4VSPJJJY6P88Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXJJXPJ1EWF19V6HRK6FT04W</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ITSM Configuration</t>
+          <t>JML Ticket Creation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KXJJN9VZBHQGB4Y7630BXC6D</t>
+          <t>h_01KX61939S4SZ5BEVCQHTG9E7H</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXJJN9VZBHQGB4Y7630BXC6D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX61939S4SZ5BEVCQHTG9E7H</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Messaging Applications</t>
+          <t>Ticket Creation Configuration</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,107 +825,107 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KXJJXPJ1EWF19V6HRK6FT04W</t>
+          <t>h_01KX62FZ36XZ8CYT2AKJYB3PBY</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXJJXPJ1EWF19V6HRK6FT04W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX62FZ36XZ8CYT2AKJYB3PBY</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JML Ticket Creation</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KX61939S4SZ5BEVCQHTG9E7H</t>
+          <t>h_01KXD24R6KTK64TSFZQ15WSWQC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX61939S4SZ5BEVCQHTG9E7H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD24R6KTK64TSFZQ15WSWQC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ticket Creation Configuration</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KX62FZ36XZ8CYT2AKJYB3PBY</t>
+          <t>h_01KXD2651GJMQ6D9TWKV4SSSP3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KX62FZ36XZ8CYT2AKJYB3PBY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD2651GJMQ6D9TWKV4SSSP3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Define notification channel</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KXD24R6KTK64TSFZQ15WSWQC</t>
+          <t>h_01KXD26T3P58PTGRVFB8TYXY4P</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD24R6KTK64TSFZQ15WSWQC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD26T3P58PTGRVFB8TYXY4P</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Notification Configuration</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KXD2651GJMQ6D9TWKV4SSSP3</t>
+          <t>h_01KXD29HX4PNGN0WXCW65Q1XRH</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD2651GJMQ6D9TWKV4SSSP3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD29HX4PNGN0WXCW65Q1XRH</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Define notification channel</t>
+          <t>Global Operational Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KXD26T3P58PTGRVFB8TYXY4P</t>
+          <t>h_01KXD2QFV2YDHGWHC3WSPM2901</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD26T3P58PTGRVFB8TYXY4P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD2QFV2YDHGWHC3WSPM2901</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Notification Configuration</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,41 +957,41 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KXD29HX4PNGN0WXCW65Q1XRH</t>
+          <t>h_01KXD2TCEBQ7ZZR8FH8MDKYFAY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD29HX4PNGN0WXCW65Q1XRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD2TCEBQ7ZZR8FH8MDKYFAY</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Global Operational Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KXD2QFV2YDHGWHC3WSPM2901</t>
+          <t>h_01KXD2WYEFJZWHVJ7J2HGG6R6Q</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD2QFV2YDHGWHC3WSPM2901</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD2WYEFJZWHVJ7J2HGG6R6Q</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,78 +1001,78 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KXD2TCEBQ7ZZR8FH8MDKYFAY</t>
+          <t>h_01KXD3N3VJF9FQZ3SK744FQMJX</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD2TCEBQ7ZZR8FH8MDKYFAY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD3N3VJF9FQZ3SK744FQMJX</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KXD2WYEFJZWHVJ7J2HGG6R6Q</t>
+          <t>h_01KXD3P72ED6QQD6AFJXQMHSG5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD2WYEFJZWHVJ7J2HGG6R6Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD3P72ED6QQD6AFJXQMHSG5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KXD3N3VJF9FQZ3SK744FQMJX</t>
+          <t>h_01KXD3QARYZQSR9SSX7G475QJ4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD3N3VJF9FQZ3SK744FQMJX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD3QARYZQSR9SSX7G475QJ4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Operation Safeguard Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KXD3P72ED6QQD6AFJXQMHSG5</t>
+          <t>h_01KXD3X0JENXFZJ36P50T7KRF2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD3P72ED6QQD6AFJXQMHSG5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD3X0JENXFZJ36P50T7KRF2</t>
         </is>
       </c>
     </row>
@@ -1084,147 +1084,103 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KXD3QARYZQSR9SSX7G475QJ4</t>
+          <t>h_01KXD4124NATJ17W8BA57FW3K4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD3QARYZQSR9SSX7G475QJ4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD4124NATJ17W8BA57FW3K4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Operation Safeguard Settings</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KXD3X0JENXFZJ36P50T7KRF2</t>
+          <t>h_01KXD464107EABVR5YHHD9564T</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD3X0JENXFZJ36P50T7KRF2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD464107EABVR5YHHD9564T</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KXD4124NATJ17W8BA57FW3K4</t>
+          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD4124NATJ17W8BA57FW3K4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KXD464107EABVR5YHHD9564T</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KXD464107EABVR5YHHD9564T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Execute Integration</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-HaloITSM-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
